--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111601</v>
+        <v>111603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108309</v>
+        <v>108311</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104827</v>
+        <v>104829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104827</v>
+        <v>104829</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104827</v>
+        <v>104829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107003</v>
+        <v>107005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107710</v>
+        <v>107712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107251</v>
+        <v>107253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107251</v>
+        <v>107253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100346</v>
+        <v>100348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111603</v>
+        <v>111604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99269</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108311</v>
+        <v>108312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104829</v>
+        <v>104830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104829</v>
+        <v>104830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104829</v>
+        <v>104830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107005</v>
+        <v>107006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107712</v>
+        <v>107713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107253</v>
+        <v>107254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107253</v>
+        <v>107254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100348</v>
+        <v>100349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136065647</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136065648</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136065649</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136065650</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136065651</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>136065652</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111604</v>
+        <v>111605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99297</v>
+        <v>99298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108312</v>
+        <v>108313</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104830</v>
+        <v>104831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104830</v>
+        <v>104831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104830</v>
+        <v>104831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107006</v>
+        <v>107007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106332</v>
+        <v>106333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107713</v>
+        <v>107714</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107254</v>
+        <v>107255</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107254</v>
+        <v>107255</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100349</v>
+        <v>100350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136065647</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136065648</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136065649</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136065650</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136065651</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>136065652</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111605</v>
+        <v>111611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99281</v>
+        <v>99287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99298</v>
+        <v>99304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108313</v>
+        <v>108319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104831</v>
+        <v>104837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104831</v>
+        <v>104837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104831</v>
+        <v>104837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107007</v>
+        <v>107013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106333</v>
+        <v>106339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107714</v>
+        <v>107720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107255</v>
+        <v>107261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107255</v>
+        <v>107261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100350</v>
+        <v>100356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136065647</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136065648</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136065649</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136065650</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>136065651</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>136065652</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111611</v>
+        <v>111612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99277</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99287</v>
+        <v>99288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99304</v>
+        <v>99305</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104837</v>
+        <v>104838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104837</v>
+        <v>104838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104837</v>
+        <v>104838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110282</v>
+        <v>110283</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107013</v>
+        <v>107014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106339</v>
+        <v>106340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107720</v>
+        <v>107721</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107720</v>
+        <v>107721</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107261</v>
+        <v>107262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107261</v>
+        <v>107262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100356</v>
+        <v>100357</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
